--- a/artfynd/S 432-2026 artfynd.xlsx
+++ b/artfynd/S 432-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104230095</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431625</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14448843</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58219906</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57033773</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431647</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57197818</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57040251</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62732900</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15007073</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1831,6 +1886,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57237856</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1942,6 +2002,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62193885</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2039,6 +2104,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62193886</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62127065</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2243,6 +2318,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62536638</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2362,6 +2442,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118095918</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,6 +2554,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254157</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2576,6 +2666,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254158</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2683,6 +2778,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254159</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2780,6 +2880,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114280905</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2877,6 +2982,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114280906</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2984,6 +3094,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119253819</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3095,6 +3210,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254044</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3202,6 +3322,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254163</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3309,6 +3434,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119254164</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3411,6 +3541,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62123691</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3508,6 +3643,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62303391</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3605,6 +3745,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082557</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3707,6 +3852,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62082560</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3814,6 +3964,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62505206</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3934,6 +4089,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045762</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4062,6 +4222,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045761</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4181,6 +4346,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045759</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4300,6 +4470,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045758</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4424,6 +4599,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045764</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4544,6 +4724,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045763</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4663,6 +4848,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045770</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4782,6 +4972,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045772</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4901,6 +5096,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115045767</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5030,6 +5230,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118216554</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5159,6 +5364,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118217261</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5256,8 +5466,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431666</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>